--- a/Data_Collection_AMOS_Ready_Final.xlsx
+++ b/Data_Collection_AMOS_Ready_Final.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\soharr\Desktop\GWU\Praxis Chapters\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\soharr\Desktop\GWU\Summer 2026\Session 5\Github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{15196248-0138-463F-B3A5-4E69CFCADB67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56D06B16-15FA-4B9D-9929-2BF3EF2EB976}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="2145" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Complete Dataset" sheetId="1" r:id="rId1"/>
@@ -1905,10 +1905,19 @@
     <xf numFmtId="0" fontId="29" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1919,15 +1928,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2267,7 +2267,7 @@
   <sheetData>
     <row r="1" spans="1:20" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="1:20" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="51" t="s">
+      <c r="A2" s="45" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="46"/>
@@ -2291,7 +2291,7 @@
       <c r="T2" s="46"/>
     </row>
     <row r="3" spans="1:20" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="48" t="s">
+      <c r="A3" s="51" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="46"/>
@@ -2315,33 +2315,33 @@
       <c r="T3" s="46"/>
     </row>
     <row r="4" spans="1:20" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="53" t="s">
+      <c r="A4" s="48" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="46"/>
       <c r="C4" s="46"/>
-      <c r="D4" s="49" t="s">
+      <c r="D4" s="52" t="s">
         <v>3</v>
       </c>
       <c r="E4" s="46"/>
       <c r="F4" s="46"/>
-      <c r="G4" s="50" t="s">
+      <c r="G4" s="53" t="s">
         <v>4</v>
       </c>
       <c r="H4" s="46"/>
       <c r="I4" s="46"/>
-      <c r="J4" s="52" t="s">
+      <c r="J4" s="47" t="s">
         <v>5</v>
       </c>
       <c r="K4" s="46"/>
       <c r="L4" s="46"/>
-      <c r="M4" s="45" t="s">
+      <c r="M4" s="49" t="s">
         <v>6</v>
       </c>
       <c r="N4" s="46"/>
       <c r="O4" s="46"/>
       <c r="P4" s="46"/>
-      <c r="Q4" s="47" t="s">
+      <c r="Q4" s="50" t="s">
         <v>7</v>
       </c>
       <c r="R4" s="46"/>
@@ -14659,7 +14659,7 @@
       <c r="J2" s="46"/>
     </row>
     <row r="3" spans="1:10" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="48" t="s">
+      <c r="A3" s="51" t="s">
         <v>420</v>
       </c>
       <c r="B3" s="46"/>
@@ -21046,7 +21046,7 @@
       <c r="L2" s="46"/>
     </row>
     <row r="3" spans="1:12" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="48" t="s">
+      <c r="A3" s="51" t="s">
         <v>432</v>
       </c>
       <c r="B3" s="46"/>
